--- a/AAII_Financials/Quarterly/EPOBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EPOBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
   <si>
     <t>EPOBY</t>
   </si>
@@ -656,61 +656,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -738,8 +742,11 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -767,8 +774,11 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -796,8 +806,11 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,8 +822,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -838,8 +852,11 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,8 +884,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -896,8 +916,11 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -925,8 +948,11 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,8 +961,9 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -964,8 +991,11 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -993,8 +1023,11 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,8 +1039,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1035,8 +1069,11 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1064,8 +1101,11 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1093,8 +1133,11 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1122,8 +1165,11 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1151,8 +1197,11 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,8 +1229,11 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1209,8 +1261,11 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1238,8 +1293,11 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1325,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1357,11 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1389,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,8 +1421,11 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1383,8 +1453,11 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1412,8 +1485,11 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,8 +1517,11 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1470,42 +1549,48 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1602,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,42 +1616,46 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>805400</v>
+      </c>
+      <c r="E41" s="3">
         <v>907300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>648700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>702900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>622500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1298100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>636500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>580900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>458700</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>141400</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -1577,222 +1667,246 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>138400</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>149500</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1821800</v>
+      </c>
+      <c r="E43" s="3">
         <v>1658200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1591500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1561200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1488500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1351100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1464300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1369100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1430000</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1894800</v>
+      </c>
+      <c r="E44" s="3">
         <v>1820400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1734000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1991800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2016500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1925900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1864100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1838100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1868400</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3">
         <v>166400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>20900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>129700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>139900</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>50900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>151800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4663400</v>
+      </c>
+      <c r="E46" s="3">
         <v>4552300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4084500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4385600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4267500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4713400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4088800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3939900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3915700</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3100</v>
+        <v>243400</v>
       </c>
       <c r="E47" s="3">
+        <v>194200</v>
+      </c>
+      <c r="F47" s="3">
         <v>5800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2700</v>
       </c>
-      <c r="G47" s="3">
-        <v>2600</v>
-      </c>
       <c r="H47" s="3">
+        <v>169100</v>
+      </c>
+      <c r="I47" s="3">
         <v>172300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>199800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>188700</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>936400</v>
+      </c>
+      <c r="E48" s="3">
         <v>884800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>856100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>902000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>895900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>740200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>757100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>690200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>700800</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2350200</v>
+      </c>
+      <c r="E49" s="3">
         <v>2287600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2265700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2379200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2160300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1513600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1575400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1511500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1564200</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +1934,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,37 +1966,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>191100</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3">
         <v>153900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>219500</v>
       </c>
-      <c r="G52" s="3">
-        <v>166400</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3">
         <v>118200</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2030,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8344600</v>
+      </c>
+      <c r="E54" s="3">
         <v>8054500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7552800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8042000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7643800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7288900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6740200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6482200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6515700</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2078,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,182 +2092,201 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>620400</v>
+      </c>
+      <c r="E57" s="3">
         <v>554300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>520100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>523900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>580300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>581100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>586900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>569900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>667000</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>450000</v>
+      </c>
+      <c r="E58" s="3">
         <v>236900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>217300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>440700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>428100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>213700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>214100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>284100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>354700</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1211300</v>
+      </c>
+      <c r="E59" s="3">
         <v>919900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>497700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1166500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1139200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>866300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>534600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1073400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1097100</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2281700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1711100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1649200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2131200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2147600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1661100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1690700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1927400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2118900</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1794800</v>
+      </c>
+      <c r="E61" s="3">
         <v>1892000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1772100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1779800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1696100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1654900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1175500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>990900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>958800</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E62" s="3">
         <v>54500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>54800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>62600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>53100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>56800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>57300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>54900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>64000</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2314,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2346,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2378,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4285900</v>
+      </c>
+      <c r="E66" s="3">
         <v>3823500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3651200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4134700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4048700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3476400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3040200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3073800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3252500</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2426,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2456,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2488,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +2520,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2552,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4004400</v>
+      </c>
+      <c r="E72" s="3">
         <v>4144500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3609500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3818200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3509600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3728600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3525200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3316400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3170100</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2616,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2648,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2680,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4056900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4194300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3863400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3867500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3556800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3775400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3661400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3362300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3216400</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,42 +2744,48 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2618,8 +2813,11 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,37 +2829,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>74300</v>
+      </c>
+      <c r="E83" s="3">
         <v>62900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>34200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>64300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>59700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>61300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>47400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>47500</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +2891,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +2923,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +2955,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +2987,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3019,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>223100</v>
+      </c>
+      <c r="E89" s="3">
         <v>257800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>356400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>246600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>152000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>224800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>277700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>175900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>157000</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,37 +3067,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-31500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-26800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-24800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-19800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-20100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-36700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3129,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +3161,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-28000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-67400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-170600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-821100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-47800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-35100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-34000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-71700</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,37 +3209,41 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>241400</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3">
         <v>207500</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3">
         <v>216500</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
         <v>204000</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3">
         <v>190100</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3271,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3303,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,91 +3335,103 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-293600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-293700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-17500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>509800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-218400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-59900</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
         <v>12500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-17200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-5500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-16400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-152300</v>
+      </c>
+      <c r="E102" s="3">
         <v>192100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>52400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-687000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>699400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>126700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>33600</v>
       </c>
     </row>
